--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -22713,21 +22701,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Mexico WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Coverage: 2022-11-15 to 2026-03-22 | Publication days: 741</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -22735,22 +22723,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -22266,13 +22266,13 @@
         </is>
       </c>
       <c r="B1203" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1203" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1203" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1203" t="b">
         <v>1</v>
@@ -22288,10 +22288,10 @@
         <v>0</v>
       </c>
       <c r="C1204" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1204" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1204" t="b">
         <v>1</v>
@@ -22307,10 +22307,10 @@
         <v>0</v>
       </c>
       <c r="C1205" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1205" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1205" t="b">
         <v>1</v>
@@ -22324,10 +22324,10 @@
       </c>
       <c r="B1206" t="inlineStr"/>
       <c r="C1206" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1206" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1206" t="b">
         <v>0</v>
@@ -22341,10 +22341,10 @@
       </c>
       <c r="B1207" t="inlineStr"/>
       <c r="C1207" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1207" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1207" t="b">
         <v>0</v>
@@ -22360,10 +22360,10 @@
         <v>-2</v>
       </c>
       <c r="C1208" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1208" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1208" t="b">
         <v>1</v>
@@ -22379,10 +22379,10 @@
         <v>0</v>
       </c>
       <c r="C1209" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1209" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1209" t="b">
         <v>1</v>
@@ -22401,7 +22401,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1210" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1210" t="b">
         <v>1</v>
@@ -22418,7 +22418,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1211" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1211" t="b">
         <v>0</v>
@@ -22437,7 +22437,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1212" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1212" t="b">
         <v>1</v>
@@ -22456,7 +22456,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1213" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1213" t="b">
         <v>1</v>
@@ -22475,7 +22475,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1214" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1214" t="b">
         <v>1</v>
@@ -22492,7 +22492,7 @@
         <v>0</v>
       </c>
       <c r="D1215" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1215" t="b">
         <v>0</v>
@@ -22511,7 +22511,7 @@
         <v>0</v>
       </c>
       <c r="D1216" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1216" t="b">
         <v>1</v>
@@ -22530,7 +22530,7 @@
         <v>0</v>
       </c>
       <c r="D1217" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1217" t="b">
         <v>1</v>
@@ -22547,7 +22547,7 @@
         <v>0</v>
       </c>
       <c r="D1218" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1218" t="b">
         <v>0</v>
@@ -22566,7 +22566,7 @@
         <v>0</v>
       </c>
       <c r="D1219" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1219" t="b">
         <v>1</v>
@@ -22585,7 +22585,7 @@
         <v>0</v>
       </c>
       <c r="D1220" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1220" t="b">
         <v>1</v>
@@ -22602,7 +22602,7 @@
         <v>0</v>
       </c>
       <c r="D1221" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1221" t="b">
         <v>0</v>
@@ -22621,7 +22621,7 @@
         <v>0</v>
       </c>
       <c r="D1222" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1222" t="b">
         <v>1</v>
@@ -22638,7 +22638,7 @@
         <v>0</v>
       </c>
       <c r="D1223" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1223" t="b">
         <v>0</v>
@@ -22657,7 +22657,7 @@
         <v>0</v>
       </c>
       <c r="D1224" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1224" t="b">
         <v>1</v>
@@ -22674,7 +22674,7 @@
         <v>0</v>
       </c>
       <c r="D1225" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1225" t="b">
         <v>0</v>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1225"/>
+  <dimension ref="A1:E1226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22266,13 +22266,13 @@
         </is>
       </c>
       <c r="B1203" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1203" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1203" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1203" t="b">
         <v>1</v>
@@ -22288,10 +22288,10 @@
         <v>0</v>
       </c>
       <c r="C1204" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1204" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1204" t="b">
         <v>1</v>
@@ -22307,10 +22307,10 @@
         <v>0</v>
       </c>
       <c r="C1205" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1205" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1205" t="b">
         <v>1</v>
@@ -22324,10 +22324,10 @@
       </c>
       <c r="B1206" t="inlineStr"/>
       <c r="C1206" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1206" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1206" t="b">
         <v>0</v>
@@ -22341,10 +22341,10 @@
       </c>
       <c r="B1207" t="inlineStr"/>
       <c r="C1207" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1207" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1207" t="b">
         <v>0</v>
@@ -22360,10 +22360,10 @@
         <v>-2</v>
       </c>
       <c r="C1208" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1208" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1208" t="b">
         <v>1</v>
@@ -22379,10 +22379,10 @@
         <v>0</v>
       </c>
       <c r="C1209" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1209" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1209" t="b">
         <v>1</v>
@@ -22401,7 +22401,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1210" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1210" t="b">
         <v>1</v>
@@ -22418,7 +22418,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1211" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1211" t="b">
         <v>0</v>
@@ -22437,7 +22437,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1212" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1212" t="b">
         <v>1</v>
@@ -22456,7 +22456,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1213" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1213" t="b">
         <v>1</v>
@@ -22475,7 +22475,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1214" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1214" t="b">
         <v>1</v>
@@ -22492,7 +22492,7 @@
         <v>0</v>
       </c>
       <c r="D1215" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1215" t="b">
         <v>0</v>
@@ -22511,7 +22511,7 @@
         <v>0</v>
       </c>
       <c r="D1216" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1216" t="b">
         <v>1</v>
@@ -22530,7 +22530,7 @@
         <v>0</v>
       </c>
       <c r="D1217" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1217" t="b">
         <v>1</v>
@@ -22547,7 +22547,7 @@
         <v>0</v>
       </c>
       <c r="D1218" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1218" t="b">
         <v>0</v>
@@ -22566,7 +22566,7 @@
         <v>0</v>
       </c>
       <c r="D1219" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1219" t="b">
         <v>1</v>
@@ -22585,7 +22585,7 @@
         <v>0</v>
       </c>
       <c r="D1220" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1220" t="b">
         <v>1</v>
@@ -22602,7 +22602,7 @@
         <v>0</v>
       </c>
       <c r="D1221" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1221" t="b">
         <v>0</v>
@@ -22621,7 +22621,7 @@
         <v>0</v>
       </c>
       <c r="D1222" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1222" t="b">
         <v>1</v>
@@ -22638,7 +22638,7 @@
         <v>0</v>
       </c>
       <c r="D1223" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1223" t="b">
         <v>0</v>
@@ -22657,7 +22657,7 @@
         <v>0</v>
       </c>
       <c r="D1224" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1224" t="b">
         <v>1</v>
@@ -22674,9 +22674,26 @@
         <v>0</v>
       </c>
       <c r="D1225" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1225" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr"/>
+      <c r="C1226" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1226" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E1226" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22710,7 +22727,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-03-22 | Publication days: 741</t>
+          <t>Coverage: 2022-11-15 to 2026-03-23 | Publication days: 741</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1226"/>
+  <dimension ref="A1:E1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22694,6 +22694,23 @@
         <v>-0.06666666666666667</v>
       </c>
       <c r="E1226" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr"/>
+      <c r="C1227" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E1227" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22727,7 +22744,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-03-23 | Publication days: 741</t>
+          <t>Coverage: 2022-11-15 to 2026-03-24 | Publication days: 741</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1227"/>
+  <dimension ref="A1:E1228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22711,6 +22711,23 @@
         <v>-0.06666666666666667</v>
       </c>
       <c r="E1227" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr"/>
+      <c r="C1228" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E1228" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22744,7 +22761,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-03-24 | Publication days: 741</t>
+          <t>Coverage: 2022-11-15 to 2026-03-25 | Publication days: 741</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -22686,15 +22686,17 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="B1226" t="inlineStr"/>
+      <c r="B1226" t="n">
+        <v>3</v>
+      </c>
       <c r="C1226" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1226" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1226" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1227">
@@ -22703,15 +22705,17 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="B1227" t="inlineStr"/>
+      <c r="B1227" t="n">
+        <v>0</v>
+      </c>
       <c r="C1227" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1227" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1228">
@@ -22722,10 +22726,10 @@
       </c>
       <c r="B1228" t="inlineStr"/>
       <c r="C1228" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1228" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1228" t="b">
         <v>0</v>
@@ -22761,7 +22765,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-03-25 | Publication days: 741</t>
+          <t>Coverage: 2022-11-15 to 2026-03-25 | Publication days: 743</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -22756,21 +22768,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Mexico WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2022-11-15 to 2026-03-25 | Publication days: 743</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -22778,22 +22790,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1228"/>
+  <dimension ref="A1:E1229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -22744,6 +22732,23 @@
         <v>0.03333333333333333</v>
       </c>
       <c r="E1228" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr"/>
+      <c r="C1229" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E1229" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22768,21 +22773,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Mexico WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2022-11-15 to 2026-03-25 | Publication days: 743</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2022-11-15 to 2026-03-26 | Publication days: 743</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -22790,22 +22795,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -22773,21 +22785,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Mexico WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2022-11-15 to 2026-03-26 | Publication days: 743</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -22795,22 +22807,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -22736,7 +22724,9 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="B1228" t="inlineStr"/>
+      <c r="B1228" t="n">
+        <v>0</v>
+      </c>
       <c r="C1228" t="n">
         <v>0.4285714285714285</v>
       </c>
@@ -22744,7 +22734,7 @@
         <v>0.03333333333333333</v>
       </c>
       <c r="E1228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1229">
@@ -22785,21 +22775,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Mexico WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2022-11-15 to 2026-03-26 | Publication days: 743</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2022-11-15 to 2026-03-26 | Publication days: 744</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -22807,22 +22797,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -22775,21 +22787,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Mexico WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2022-11-15 to 2026-03-26 | Publication days: 744</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -22797,22 +22809,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1229"/>
+  <dimension ref="A1:E1230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -22763,6 +22751,23 @@
         <v>0.03333333333333333</v>
       </c>
       <c r="E1229" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr"/>
+      <c r="C1230" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="D1230" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E1230" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22787,21 +22792,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Mexico WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2022-11-15 to 2026-03-26 | Publication days: 744</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2022-11-15 to 2026-03-27 | Publication days: 744</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -22809,22 +22814,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -22743,7 +22743,9 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="B1229" t="inlineStr"/>
+      <c r="B1229" t="n">
+        <v>0</v>
+      </c>
       <c r="C1229" t="n">
         <v>0.4285714285714285</v>
       </c>
@@ -22751,7 +22753,7 @@
         <v>0.03333333333333333</v>
       </c>
       <c r="E1229" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1230">
@@ -22801,7 +22803,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-03-27 | Publication days: 744</t>
+          <t>Coverage: 2022-11-15 to 2026-03-27 | Publication days: 745</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1230"/>
+  <dimension ref="A1:E1231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22762,7 +22762,9 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B1230" t="inlineStr"/>
+      <c r="B1230" t="n">
+        <v>0</v>
+      </c>
       <c r="C1230" t="n">
         <v>0.4285714285714285</v>
       </c>
@@ -22770,6 +22772,23 @@
         <v>0.03333333333333333</v>
       </c>
       <c r="E1230" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr"/>
+      <c r="C1231" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E1231" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22803,7 +22822,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-03-27 | Publication days: 745</t>
+          <t>Coverage: 2022-11-15 to 2026-03-28 | Publication days: 746</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1231"/>
+  <dimension ref="A1:E1232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22789,6 +22789,23 @@
         <v>0.03333333333333333</v>
       </c>
       <c r="E1231" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr"/>
+      <c r="C1232" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="D1232" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E1232" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22822,7 +22839,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-03-28 | Publication days: 746</t>
+          <t>Coverage: 2022-11-15 to 2026-03-29 | Publication days: 746</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1232"/>
+  <dimension ref="A1:E1233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22806,6 +22806,23 @@
         <v>0.03333333333333333</v>
       </c>
       <c r="E1232" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr"/>
+      <c r="C1233" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1233" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E1233" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22839,7 +22856,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-03-29 | Publication days: 746</t>
+          <t>Coverage: 2022-11-15 to 2026-03-30 | Publication days: 746</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1233"/>
+  <dimension ref="A1:E1234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22687,13 +22687,13 @@
         </is>
       </c>
       <c r="B1226" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C1226" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1226" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1226" t="b">
         <v>1</v>
@@ -22709,10 +22709,10 @@
         <v>0</v>
       </c>
       <c r="C1227" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1227" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1227" t="b">
         <v>1</v>
@@ -22728,10 +22728,10 @@
         <v>0</v>
       </c>
       <c r="C1228" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1228" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1228" t="b">
         <v>1</v>
@@ -22747,10 +22747,10 @@
         <v>0</v>
       </c>
       <c r="C1229" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1229" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1229" t="b">
         <v>1</v>
@@ -22766,10 +22766,10 @@
         <v>0</v>
       </c>
       <c r="C1230" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1230" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1230" t="b">
         <v>1</v>
@@ -22783,10 +22783,10 @@
       </c>
       <c r="B1231" t="inlineStr"/>
       <c r="C1231" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1231" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1231" t="b">
         <v>0</v>
@@ -22800,10 +22800,10 @@
       </c>
       <c r="B1232" t="inlineStr"/>
       <c r="C1232" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1232" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1232" t="b">
         <v>0</v>
@@ -22815,14 +22815,33 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="B1233" t="inlineStr"/>
+      <c r="B1233" t="n">
+        <v>0</v>
+      </c>
       <c r="C1233" t="n">
         <v>0</v>
       </c>
       <c r="D1233" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1233" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr"/>
+      <c r="C1234" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1234" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E1234" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22856,7 +22875,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-03-30 | Publication days: 746</t>
+          <t>Coverage: 2022-11-15 to 2026-03-31 | Publication days: 747</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1234"/>
+  <dimension ref="A1:E1235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22834,7 +22834,9 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="B1234" t="inlineStr"/>
+      <c r="B1234" t="n">
+        <v>0</v>
+      </c>
       <c r="C1234" t="n">
         <v>0</v>
       </c>
@@ -22842,6 +22844,23 @@
         <v>-0.06666666666666667</v>
       </c>
       <c r="E1234" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr"/>
+      <c r="C1235" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1235" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E1235" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22875,7 +22894,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-03-31 | Publication days: 747</t>
+          <t>Coverage: 2022-11-15 to 2026-04-01 | Publication days: 748</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1235"/>
+  <dimension ref="A1:E1236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22175,13 +22175,13 @@
         </is>
       </c>
       <c r="B1198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1198" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1198" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1198" t="b">
         <v>1</v>
@@ -22197,10 +22197,10 @@
         <v>0</v>
       </c>
       <c r="C1199" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1199" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1199" t="b">
         <v>1</v>
@@ -22216,10 +22216,10 @@
         <v>0</v>
       </c>
       <c r="C1200" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1200" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1200" t="b">
         <v>1</v>
@@ -22233,10 +22233,10 @@
       </c>
       <c r="B1201" t="inlineStr"/>
       <c r="C1201" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1201" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1201" t="b">
         <v>0</v>
@@ -22250,10 +22250,10 @@
       </c>
       <c r="B1202" t="inlineStr"/>
       <c r="C1202" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1202" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1202" t="b">
         <v>0</v>
@@ -22269,10 +22269,10 @@
         <v>0</v>
       </c>
       <c r="C1203" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1203" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1203" t="b">
         <v>1</v>
@@ -22288,10 +22288,10 @@
         <v>0</v>
       </c>
       <c r="C1204" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1204" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1204" t="b">
         <v>1</v>
@@ -22310,7 +22310,7 @@
         <v>0</v>
       </c>
       <c r="D1205" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1205" t="b">
         <v>1</v>
@@ -22327,7 +22327,7 @@
         <v>0</v>
       </c>
       <c r="D1206" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1206" t="b">
         <v>0</v>
@@ -22344,7 +22344,7 @@
         <v>0</v>
       </c>
       <c r="D1207" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1207" t="b">
         <v>0</v>
@@ -22363,7 +22363,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1208" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1208" t="b">
         <v>1</v>
@@ -22382,7 +22382,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1209" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1209" t="b">
         <v>1</v>
@@ -22401,7 +22401,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1210" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1210" t="b">
         <v>1</v>
@@ -22418,7 +22418,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1211" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1211" t="b">
         <v>0</v>
@@ -22437,7 +22437,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1212" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1212" t="b">
         <v>1</v>
@@ -22456,7 +22456,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1213" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1213" t="b">
         <v>1</v>
@@ -22475,7 +22475,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1214" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1214" t="b">
         <v>1</v>
@@ -22492,7 +22492,7 @@
         <v>0</v>
       </c>
       <c r="D1215" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1215" t="b">
         <v>0</v>
@@ -22511,7 +22511,7 @@
         <v>0</v>
       </c>
       <c r="D1216" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1216" t="b">
         <v>1</v>
@@ -22530,7 +22530,7 @@
         <v>0</v>
       </c>
       <c r="D1217" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1217" t="b">
         <v>1</v>
@@ -22547,7 +22547,7 @@
         <v>0</v>
       </c>
       <c r="D1218" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1218" t="b">
         <v>0</v>
@@ -22566,7 +22566,7 @@
         <v>0</v>
       </c>
       <c r="D1219" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1219" t="b">
         <v>1</v>
@@ -22585,7 +22585,7 @@
         <v>0</v>
       </c>
       <c r="D1220" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1220" t="b">
         <v>1</v>
@@ -22602,7 +22602,7 @@
         <v>0</v>
       </c>
       <c r="D1221" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1221" t="b">
         <v>0</v>
@@ -22621,7 +22621,7 @@
         <v>0</v>
       </c>
       <c r="D1222" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1222" t="b">
         <v>1</v>
@@ -22638,7 +22638,7 @@
         <v>0</v>
       </c>
       <c r="D1223" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1223" t="b">
         <v>0</v>
@@ -22657,7 +22657,7 @@
         <v>0</v>
       </c>
       <c r="D1224" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1224" t="b">
         <v>1</v>
@@ -22674,7 +22674,7 @@
         <v>0</v>
       </c>
       <c r="D1225" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1225" t="b">
         <v>0</v>
@@ -22693,7 +22693,7 @@
         <v>0</v>
       </c>
       <c r="D1226" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1226" t="b">
         <v>1</v>
@@ -22712,7 +22712,7 @@
         <v>0</v>
       </c>
       <c r="D1227" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1227" t="b">
         <v>1</v>
@@ -22861,6 +22861,23 @@
         <v>-0.06666666666666667</v>
       </c>
       <c r="E1235" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr"/>
+      <c r="C1236" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1236" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E1236" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22894,7 +22911,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-04-01 | Publication days: 748</t>
+          <t>Coverage: 2022-11-15 to 2026-04-02 | Publication days: 748</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1236"/>
+  <dimension ref="A1:E1237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22870,7 +22870,9 @@
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="B1236" t="inlineStr"/>
+      <c r="B1236" t="n">
+        <v>0</v>
+      </c>
       <c r="C1236" t="n">
         <v>0</v>
       </c>
@@ -22878,6 +22880,23 @@
         <v>-0.06666666666666667</v>
       </c>
       <c r="E1236" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr"/>
+      <c r="C1237" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1237" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E1237" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22911,7 +22930,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-04-02 | Publication days: 748</t>
+          <t>Coverage: 2022-11-15 to 2026-04-03 | Publication days: 749</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1237"/>
+  <dimension ref="A1:E1238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22897,6 +22897,23 @@
         <v>-0.06666666666666667</v>
       </c>
       <c r="E1237" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr"/>
+      <c r="C1238" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1238" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1238" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22930,7 +22947,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-04-03 | Publication days: 749</t>
+          <t>Coverage: 2022-11-15 to 2026-04-04 | Publication days: 749</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1238"/>
+  <dimension ref="A1:E1239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22914,6 +22914,23 @@
         <v>0</v>
       </c>
       <c r="E1238" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr"/>
+      <c r="C1239" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1239" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1239" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22947,7 +22964,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-04-04 | Publication days: 749</t>
+          <t>Coverage: 2022-11-15 to 2026-04-05 | Publication days: 749</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1239"/>
+  <dimension ref="A1:E1240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22931,6 +22931,23 @@
         <v>0</v>
       </c>
       <c r="E1239" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr"/>
+      <c r="C1240" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1240" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22964,7 +22981,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-04-05 | Publication days: 749</t>
+          <t>Coverage: 2022-11-15 to 2026-04-06 | Publication days: 749</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1240"/>
+  <dimension ref="A1:E1241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22687,13 +22687,13 @@
         </is>
       </c>
       <c r="B1226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1226" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1226" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1226" t="b">
         <v>1</v>
@@ -22709,10 +22709,10 @@
         <v>0</v>
       </c>
       <c r="C1227" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1227" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1227" t="b">
         <v>1</v>
@@ -22728,10 +22728,10 @@
         <v>0</v>
       </c>
       <c r="C1228" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1228" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1228" t="b">
         <v>1</v>
@@ -22747,10 +22747,10 @@
         <v>0</v>
       </c>
       <c r="C1229" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1229" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1229" t="b">
         <v>1</v>
@@ -22766,10 +22766,10 @@
         <v>0</v>
       </c>
       <c r="C1230" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1230" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1230" t="b">
         <v>1</v>
@@ -22783,10 +22783,10 @@
       </c>
       <c r="B1231" t="inlineStr"/>
       <c r="C1231" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1231" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1231" t="b">
         <v>0</v>
@@ -22800,10 +22800,10 @@
       </c>
       <c r="B1232" t="inlineStr"/>
       <c r="C1232" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1232" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1232" t="b">
         <v>0</v>
@@ -22822,7 +22822,7 @@
         <v>0</v>
       </c>
       <c r="D1233" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1233" t="b">
         <v>1</v>
@@ -22841,7 +22841,7 @@
         <v>0</v>
       </c>
       <c r="D1234" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1234" t="b">
         <v>1</v>
@@ -22858,7 +22858,7 @@
         <v>0</v>
       </c>
       <c r="D1235" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1235" t="b">
         <v>0</v>
@@ -22877,7 +22877,7 @@
         <v>0</v>
       </c>
       <c r="D1236" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1236" t="b">
         <v>1</v>
@@ -22894,7 +22894,7 @@
         <v>0</v>
       </c>
       <c r="D1237" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1237" t="b">
         <v>0</v>
@@ -22911,7 +22911,7 @@
         <v>0</v>
       </c>
       <c r="D1238" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1238" t="b">
         <v>0</v>
@@ -22928,7 +22928,7 @@
         <v>0</v>
       </c>
       <c r="D1239" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1239" t="b">
         <v>0</v>
@@ -22940,14 +22940,33 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="B1240" t="inlineStr"/>
+      <c r="B1240" t="n">
+        <v>0</v>
+      </c>
       <c r="C1240" t="n">
         <v>0</v>
       </c>
       <c r="D1240" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1240" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr"/>
+      <c r="C1241" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1241" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="E1241" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22981,7 +23000,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-04-06 | Publication days: 749</t>
+          <t>Coverage: 2022-11-15 to 2026-04-07 | Publication days: 750</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1241"/>
+  <dimension ref="A1:E1242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22967,6 +22967,23 @@
         <v>0.06666666666666667</v>
       </c>
       <c r="E1241" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr"/>
+      <c r="C1242" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1242" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="E1242" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23000,7 +23017,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-04-07 | Publication days: 750</t>
+          <t>Coverage: 2022-11-15 to 2026-04-08 | Publication days: 750</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1242"/>
+  <dimension ref="A1:E1243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22266,13 +22266,13 @@
         </is>
       </c>
       <c r="B1203" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1203" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1203" t="n">
-        <v>0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1203" t="b">
         <v>1</v>
@@ -22288,10 +22288,10 @@
         <v>0</v>
       </c>
       <c r="C1204" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1204" t="n">
-        <v>0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1204" t="b">
         <v>1</v>
@@ -22307,10 +22307,10 @@
         <v>0</v>
       </c>
       <c r="C1205" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1205" t="n">
-        <v>0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1205" t="b">
         <v>1</v>
@@ -22324,10 +22324,10 @@
       </c>
       <c r="B1206" t="inlineStr"/>
       <c r="C1206" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1206" t="n">
-        <v>0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1206" t="b">
         <v>0</v>
@@ -22341,10 +22341,10 @@
       </c>
       <c r="B1207" t="inlineStr"/>
       <c r="C1207" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1207" t="n">
-        <v>0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1207" t="b">
         <v>0</v>
@@ -22360,10 +22360,10 @@
         <v>-2</v>
       </c>
       <c r="C1208" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1208" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1208" t="b">
         <v>1</v>
@@ -22379,10 +22379,10 @@
         <v>0</v>
       </c>
       <c r="C1209" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1209" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1209" t="b">
         <v>1</v>
@@ -22401,7 +22401,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1210" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1210" t="b">
         <v>1</v>
@@ -22418,7 +22418,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1211" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1211" t="b">
         <v>0</v>
@@ -22437,7 +22437,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1212" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1212" t="b">
         <v>1</v>
@@ -22456,7 +22456,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1213" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1213" t="b">
         <v>1</v>
@@ -22475,7 +22475,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1214" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1214" t="b">
         <v>1</v>
@@ -22492,7 +22492,7 @@
         <v>0</v>
       </c>
       <c r="D1215" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1215" t="b">
         <v>0</v>
@@ -22511,7 +22511,7 @@
         <v>0</v>
       </c>
       <c r="D1216" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1216" t="b">
         <v>1</v>
@@ -22530,7 +22530,7 @@
         <v>0</v>
       </c>
       <c r="D1217" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1217" t="b">
         <v>1</v>
@@ -22547,7 +22547,7 @@
         <v>0</v>
       </c>
       <c r="D1218" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1218" t="b">
         <v>0</v>
@@ -22566,7 +22566,7 @@
         <v>0</v>
       </c>
       <c r="D1219" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1219" t="b">
         <v>1</v>
@@ -22585,7 +22585,7 @@
         <v>0</v>
       </c>
       <c r="D1220" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1220" t="b">
         <v>1</v>
@@ -22602,7 +22602,7 @@
         <v>0</v>
       </c>
       <c r="D1221" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1221" t="b">
         <v>0</v>
@@ -22621,7 +22621,7 @@
         <v>0</v>
       </c>
       <c r="D1222" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1222" t="b">
         <v>1</v>
@@ -22638,7 +22638,7 @@
         <v>0</v>
       </c>
       <c r="D1223" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1223" t="b">
         <v>0</v>
@@ -22657,7 +22657,7 @@
         <v>0</v>
       </c>
       <c r="D1224" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1224" t="b">
         <v>1</v>
@@ -22674,7 +22674,7 @@
         <v>0</v>
       </c>
       <c r="D1225" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1225" t="b">
         <v>0</v>
@@ -22693,7 +22693,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1226" t="n">
-        <v>0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1226" t="b">
         <v>1</v>
@@ -22712,7 +22712,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1227" t="n">
-        <v>0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1227" t="b">
         <v>1</v>
@@ -22731,7 +22731,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1228" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1228" t="b">
         <v>1</v>
@@ -22750,7 +22750,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1229" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1229" t="b">
         <v>1</v>
@@ -22769,7 +22769,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1230" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1230" t="b">
         <v>1</v>
@@ -22786,7 +22786,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1231" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1231" t="b">
         <v>0</v>
@@ -22803,7 +22803,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1232" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1232" t="b">
         <v>0</v>
@@ -22984,6 +22984,23 @@
         <v>0.06666666666666667</v>
       </c>
       <c r="E1242" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr"/>
+      <c r="C1243" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1243" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="E1243" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23017,7 +23034,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-04-08 | Publication days: 750</t>
+          <t>Coverage: 2022-11-15 to 2026-04-09 | Publication days: 750</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1243"/>
+  <dimension ref="A1:E1244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22175,13 +22175,13 @@
         </is>
       </c>
       <c r="B1198" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1198" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1198" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1198" t="b">
         <v>1</v>
@@ -22197,10 +22197,10 @@
         <v>0</v>
       </c>
       <c r="C1199" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1199" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1199" t="b">
         <v>1</v>
@@ -22216,10 +22216,10 @@
         <v>0</v>
       </c>
       <c r="C1200" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1200" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1200" t="b">
         <v>1</v>
@@ -22233,10 +22233,10 @@
       </c>
       <c r="B1201" t="inlineStr"/>
       <c r="C1201" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1201" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1201" t="b">
         <v>0</v>
@@ -22250,10 +22250,10 @@
       </c>
       <c r="B1202" t="inlineStr"/>
       <c r="C1202" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1202" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1202" t="b">
         <v>0</v>
@@ -22269,10 +22269,10 @@
         <v>-2</v>
       </c>
       <c r="C1203" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1203" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1203" t="b">
         <v>1</v>
@@ -22288,10 +22288,10 @@
         <v>0</v>
       </c>
       <c r="C1204" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1204" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1204" t="b">
         <v>1</v>
@@ -22310,7 +22310,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1205" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1205" t="b">
         <v>1</v>
@@ -22327,7 +22327,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1206" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1206" t="b">
         <v>0</v>
@@ -22344,7 +22344,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1207" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1207" t="b">
         <v>0</v>
@@ -22363,7 +22363,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1208" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1208" t="b">
         <v>1</v>
@@ -22382,7 +22382,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1209" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1209" t="b">
         <v>1</v>
@@ -22401,7 +22401,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1210" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1210" t="b">
         <v>1</v>
@@ -22418,7 +22418,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1211" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1211" t="b">
         <v>0</v>
@@ -22437,7 +22437,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1212" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1212" t="b">
         <v>1</v>
@@ -22456,7 +22456,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1213" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1213" t="b">
         <v>1</v>
@@ -22475,7 +22475,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1214" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1214" t="b">
         <v>1</v>
@@ -22492,7 +22492,7 @@
         <v>0</v>
       </c>
       <c r="D1215" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1215" t="b">
         <v>0</v>
@@ -22511,7 +22511,7 @@
         <v>0</v>
       </c>
       <c r="D1216" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1216" t="b">
         <v>1</v>
@@ -22530,7 +22530,7 @@
         <v>0</v>
       </c>
       <c r="D1217" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1217" t="b">
         <v>1</v>
@@ -22547,7 +22547,7 @@
         <v>0</v>
       </c>
       <c r="D1218" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1218" t="b">
         <v>0</v>
@@ -22566,7 +22566,7 @@
         <v>0</v>
       </c>
       <c r="D1219" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1219" t="b">
         <v>1</v>
@@ -22585,7 +22585,7 @@
         <v>0</v>
       </c>
       <c r="D1220" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1220" t="b">
         <v>1</v>
@@ -22602,7 +22602,7 @@
         <v>0</v>
       </c>
       <c r="D1221" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1221" t="b">
         <v>0</v>
@@ -22621,7 +22621,7 @@
         <v>0</v>
       </c>
       <c r="D1222" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1222" t="b">
         <v>1</v>
@@ -22638,7 +22638,7 @@
         <v>0</v>
       </c>
       <c r="D1223" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1223" t="b">
         <v>0</v>
@@ -22657,7 +22657,7 @@
         <v>0</v>
       </c>
       <c r="D1224" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1224" t="b">
         <v>1</v>
@@ -22674,7 +22674,7 @@
         <v>0</v>
       </c>
       <c r="D1225" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1225" t="b">
         <v>0</v>
@@ -22693,7 +22693,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1226" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1226" t="b">
         <v>1</v>
@@ -22712,7 +22712,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1227" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1227" t="b">
         <v>1</v>
@@ -23001,6 +23001,23 @@
         <v>0.06666666666666667</v>
       </c>
       <c r="E1243" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr"/>
+      <c r="C1244" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1244" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="E1244" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23034,7 +23051,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-04-09 | Publication days: 750</t>
+          <t>Coverage: 2022-11-15 to 2026-04-10 | Publication days: 750</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1244"/>
+  <dimension ref="A1:E1245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23018,6 +23018,23 @@
         <v>0.06666666666666667</v>
       </c>
       <c r="E1244" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr"/>
+      <c r="C1245" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1245" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="E1245" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23051,7 +23068,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-04-10 | Publication days: 750</t>
+          <t>Coverage: 2022-11-15 to 2026-04-11 | Publication days: 750</t>
         </is>
       </c>
     </row>

--- a/data/MX.xlsx
+++ b/data/MX.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1245"/>
+  <dimension ref="A1:E1246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22266,13 +22266,13 @@
         </is>
       </c>
       <c r="B1203" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1203" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1203" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1203" t="b">
         <v>1</v>
@@ -22288,10 +22288,10 @@
         <v>0</v>
       </c>
       <c r="C1204" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1204" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1204" t="b">
         <v>1</v>
@@ -22307,10 +22307,10 @@
         <v>0</v>
       </c>
       <c r="C1205" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1205" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1205" t="b">
         <v>1</v>
@@ -22324,10 +22324,10 @@
       </c>
       <c r="B1206" t="inlineStr"/>
       <c r="C1206" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1206" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1206" t="b">
         <v>0</v>
@@ -22341,10 +22341,10 @@
       </c>
       <c r="B1207" t="inlineStr"/>
       <c r="C1207" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1207" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1207" t="b">
         <v>0</v>
@@ -22360,10 +22360,10 @@
         <v>-2</v>
       </c>
       <c r="C1208" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1208" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1208" t="b">
         <v>1</v>
@@ -22379,10 +22379,10 @@
         <v>0</v>
       </c>
       <c r="C1209" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1209" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1209" t="b">
         <v>1</v>
@@ -22401,7 +22401,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1210" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1210" t="b">
         <v>1</v>
@@ -22418,7 +22418,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1211" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1211" t="b">
         <v>0</v>
@@ -22437,7 +22437,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1212" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1212" t="b">
         <v>1</v>
@@ -22456,7 +22456,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1213" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1213" t="b">
         <v>1</v>
@@ -22475,7 +22475,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1214" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1214" t="b">
         <v>1</v>
@@ -22492,7 +22492,7 @@
         <v>0</v>
       </c>
       <c r="D1215" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1215" t="b">
         <v>0</v>
@@ -22511,7 +22511,7 @@
         <v>0</v>
       </c>
       <c r="D1216" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1216" t="b">
         <v>1</v>
@@ -22530,7 +22530,7 @@
         <v>0</v>
       </c>
       <c r="D1217" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1217" t="b">
         <v>1</v>
@@ -22547,7 +22547,7 @@
         <v>0</v>
       </c>
       <c r="D1218" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1218" t="b">
         <v>0</v>
@@ -22566,7 +22566,7 @@
         <v>0</v>
       </c>
       <c r="D1219" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1219" t="b">
         <v>1</v>
@@ -22585,7 +22585,7 @@
         <v>0</v>
       </c>
       <c r="D1220" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1220" t="b">
         <v>1</v>
@@ -22602,7 +22602,7 @@
         <v>0</v>
       </c>
       <c r="D1221" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1221" t="b">
         <v>0</v>
@@ -22621,7 +22621,7 @@
         <v>0</v>
       </c>
       <c r="D1222" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1222" t="b">
         <v>1</v>
@@ -22638,7 +22638,7 @@
         <v>0</v>
       </c>
       <c r="D1223" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1223" t="b">
         <v>0</v>
@@ -22657,7 +22657,7 @@
         <v>0</v>
       </c>
       <c r="D1224" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1224" t="b">
         <v>1</v>
@@ -22674,7 +22674,7 @@
         <v>0</v>
       </c>
       <c r="D1225" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1225" t="b">
         <v>0</v>
@@ -22693,7 +22693,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1226" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1226" t="b">
         <v>1</v>
@@ -22712,7 +22712,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1227" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1227" t="b">
         <v>1</v>
@@ -22731,7 +22731,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1228" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1228" t="b">
         <v>1</v>
@@ -22750,7 +22750,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1229" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1229" t="b">
         <v>1</v>
@@ -22769,7 +22769,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1230" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1230" t="b">
         <v>1</v>
@@ -22786,7 +22786,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1231" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1231" t="b">
         <v>0</v>
@@ -22803,7 +22803,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1232" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1232" t="b">
         <v>0</v>
@@ -23010,7 +23010,9 @@
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="B1244" t="inlineStr"/>
+      <c r="B1244" t="n">
+        <v>0</v>
+      </c>
       <c r="C1244" t="n">
         <v>0</v>
       </c>
@@ -23018,7 +23020,7 @@
         <v>0.06666666666666667</v>
       </c>
       <c r="E1244" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1245">
@@ -23027,7 +23029,9 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="B1245" t="inlineStr"/>
+      <c r="B1245" t="n">
+        <v>0</v>
+      </c>
       <c r="C1245" t="n">
         <v>0</v>
       </c>
@@ -23035,6 +23039,23 @@
         <v>0.06666666666666667</v>
       </c>
       <c r="E1245" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr"/>
+      <c r="C1246" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1246" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="E1246" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23068,7 +23089,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-11-15 to 2026-04-11 | Publication days: 750</t>
+          <t>Coverage: 2022-11-15 to 2026-04-12 | Publication days: 752</t>
         </is>
       </c>
     </row>
